--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>43588</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>44144</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>44160</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44279</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>44490</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44519</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>44602</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44658</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>44721</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>44790</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>44811</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44840</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44977</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45120</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45222</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45243</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>43332</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>43348</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>43360</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>43382</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>43403</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>43411</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>43413</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>43418</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>43418</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>43423</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>43424</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>43426</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>43430</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>43430</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>43431</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>43440</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>43447</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>43453</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43454</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>43473</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>43476</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>43478</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43479</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43480</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43481</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43482</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43486</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43486</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43489</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43489</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43493</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43495</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>43502</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>43508</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>43509</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>43510</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>43511</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>43530</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>43537</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43559</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>43559</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>43565</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>43567</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43567</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43579</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43588</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43588</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43601</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43605</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43612</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>43614</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>43623</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>43626</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>43650</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>43651</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>43662</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>43696</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>43696</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>43698</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>43700</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43706</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>43707</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>43714</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>43718</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>43719</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>43719</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>43721</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>43728</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>43728</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43732</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>43735</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>43746</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>43755</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43759</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43761</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43763</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43767</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43770</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43770</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43776</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43777</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>43777</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>43783</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>43788</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>43790</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>43794</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>43808</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>43809</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43811</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43812</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>43812</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>43818</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>43818</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>43838</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>43850</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>43852</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>43854</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>43855</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>43865</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>43871</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>43872</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>43873</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>43873</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>43879</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>43879</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>43888</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>43889</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>43895</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>43896</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>43901</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>43906</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>43927</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>43936</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>43942</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>43951</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>43955</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>43959</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>43962</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>43978</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>43979</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>43980</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>43983</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>43990</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>43990</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43997</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44000</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44000</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44005</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44006</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44008</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44011</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44014</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44015</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44015</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44022</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44025</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>44026</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>44043</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44056</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44056</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44060</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44060</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
         <v>44062</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44067</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>44068</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44068</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>44069</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44076</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44076</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44078</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44081</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>44084</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44095</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>44095</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44096</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44096</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>44098</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44109</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44112</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>44112</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>44118</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44123</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44124</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44125</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44125</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>44126</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>44126</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>44127</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>44127</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44134</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>44140</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44140</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44144</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44146</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44147</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44152</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44154</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44154</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44158</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44158</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44160</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44161</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44162</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44175</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>44176</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44176</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44191</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44191</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44192</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>44192</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>44196</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>44200</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>44200</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>44204</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44216</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44223</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44228</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44231</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44235</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44235</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44252</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44252</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44258</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44258</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44260</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44263</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44263</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44270</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44271</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>44271</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>44272</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>44272</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>44274</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>44274</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>44277</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>44278</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44279</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>44279</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44281</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44284</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44284</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>44286</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>44286</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>44294</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>44294</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>44295</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44300</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>44300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44305</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>44307</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44308</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44308</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44316</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44316</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>44319</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>44321</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>44321</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44326</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>44333</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>44334</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>44336</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>44342</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>44342</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44343</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44347</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>44349</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>44349</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>44350</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44351</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>44351</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44354</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>44356</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>44361</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>44364</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44364</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>44369</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>44369</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44370</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>44370</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44376</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44377</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44389</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44390</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44390</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44414</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>44418</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>44419</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>44421</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>44427</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>44437</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>44438</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>44439</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44445</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>44446</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44448</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44452</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44455</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44459</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22853,7 +22853,7 @@
         <v>44461</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44462</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44466</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>44466</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44468</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>44473</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44488</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44488</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44490</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>44491</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44491</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44494</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>44496</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>44497</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>44498</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>44498</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23867,7 +23867,7 @@
         <v>44502</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44516</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44517</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>44518</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24100,7 +24100,7 @@
         <v>44519</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>44519</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44523</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44526</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44533</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44538</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>44539</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44539</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44543</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>44545</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>44546</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>44546</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>44557</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>44560</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44571</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44573</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44579</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>44580</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>44585</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>44585</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>44586</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>44588</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>44589</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>44589</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>44593</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44594</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44599</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>44599</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44600</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>44603</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26212,7 +26212,7 @@
         <v>44603</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>44606</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>44606</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>44616</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44616</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44628</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44629</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44629</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44631</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>44634</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>44635</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44636</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44636</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44637</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44641</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>44651</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44651</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44655</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>44656</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>44658</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>44663</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>44663</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44671</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>44671</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>44684</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>44684</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>44691</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>44693</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44693</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>44694</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>44694</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44701</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>44706</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>44706</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>44708</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>44713</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44720</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>44733</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44733</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>44734</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>44735</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>44735</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44739</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>44741</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44742</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44749</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>44750</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44756</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44756</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44757</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44763</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44767</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44775</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44775</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44776</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44782</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44785</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44785</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44788</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44790</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>44795</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>44796</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>44800</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30890,7 +30890,7 @@
         <v>44802</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>44804</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>44804</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>44805</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31128,7 +31128,7 @@
         <v>44805</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>44810</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>44810</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>44813</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>44813</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>44817</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>44818</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>44820</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>44823</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44823</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44824</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>44827</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44830</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>44840</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>44840</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44841</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44845</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44845</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44846</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44845</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44846</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44848</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44853</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44853</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44859</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>44862</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>44865</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44865</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>44867</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>44867</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>44868</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>44869</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>44874</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>44874</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44876</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>44876</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>44881</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>44882</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         <v>44882</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44885</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44886</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>44886</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>44887</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>44888</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>44889</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>44889</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>44895</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>44895</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>44896</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>44896</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>44897</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>44904</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>44904</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>44907</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>44910</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34879,7 +34879,7 @@
         <v>44910</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>44911</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>44916</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>44922</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>44922</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44927</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>44928</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>44935</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>44935</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>44936</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>44936</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>44937</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>44937</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>44942</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44942</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44943</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44944</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>44946</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>44951</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>44951</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36277,7 +36277,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>44959</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>44959</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36986,7 +36986,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44960</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44962</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44962</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44967</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>44967</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44970</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>44971</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>44972</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>44973</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>44973</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>44979</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>44979</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>44985</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>44985</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>44986</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44988</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>44991</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>44991</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>44992</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>44994</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38466,7 +38466,7 @@
         <v>44995</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>44999</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>45006</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>45009</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45012</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45012</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45014</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45014</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45015</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45015</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45019</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45019</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45022</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39599,7 +39599,7 @@
         <v>45022</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39723,7 +39723,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         <v>45026</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39842,7 +39842,7 @@
         <v>45027</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>45027</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45029</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45029</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45030</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45030</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45034</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45034</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45036</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45036</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>45040</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45040</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45044</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45054</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45054</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45056</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>45058</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>45069</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>45070</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45071</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45071</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>45072</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45072</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>45079</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45082</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45082</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45084</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45084</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45085</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45086</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45086</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45089</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45089</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45090</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45090</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45096</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45098</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45103</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45104</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45104</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45106</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45107</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         <v>45107</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45113</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45113</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45117</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45120</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45120</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>45125</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45133</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45133</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45138</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45138</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45141</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45141</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45146</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45146</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45152</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45152</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>45156</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>45156</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>45159</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45159</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45161</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45161</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>45162</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>45162</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>45168</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45169</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44976,7 +44976,7 @@
         <v>45169</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>45176</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>45176</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45271,7 +45271,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45182</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>45182</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>45184</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45184</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45188</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45192</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>45192</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>45194</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45194</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45195</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>45195</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45196</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45197</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45198</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45203</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46327,7 +46327,7 @@
         <v>45203</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45204</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45204</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45205</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45208</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45209</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45209</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>45211</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45212</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45212</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47145,7 +47145,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45217</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45217</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45218</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47435,7 +47435,7 @@
         <v>45218</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>45219</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45219</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45220</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45223</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45223</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45224</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45229</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>45231</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45232</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45232</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48501,7 +48501,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>45238</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>45239</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>45240</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45243</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45243</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45245</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45245</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49200,7 +49200,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49262,7 +49262,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45247</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45250</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45252</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45252</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>45253</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45253</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45255</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45257</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45257</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50266,7 +50266,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45261</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45264</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45264</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45265</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45266</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45266</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45267</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45267</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45272</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45272</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45278</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45278</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45279</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45282</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45282</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45293</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45293</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45295</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45300</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45301</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45302</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52442,7 +52442,7 @@
         <v>45302</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>45303</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52566,7 +52566,7 @@
         <v>45306</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52623,7 +52623,7 @@
         <v>45308</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52680,7 +52680,7 @@
         <v>45308</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52730,14 +52730,14 @@
     <row r="866" ht="15" customHeight="1">
       <c r="A866" t="inlineStr">
         <is>
-          <t>A 2457-2024</t>
+          <t>A 2458-2024</t>
         </is>
       </c>
       <c r="B866" s="1" t="n">
         <v>45312</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52750,7 +52750,7 @@
         </is>
       </c>
       <c r="G866" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -52787,14 +52787,14 @@
     <row r="867" ht="15" customHeight="1">
       <c r="A867" t="inlineStr">
         <is>
-          <t>A 2461-2024</t>
+          <t>A 2457-2024</t>
         </is>
       </c>
       <c r="B867" s="1" t="n">
         <v>45312</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         </is>
       </c>
       <c r="G867" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="H867" t="n">
         <v>0</v>
@@ -52844,14 +52844,14 @@
     <row r="868" ht="15" customHeight="1">
       <c r="A868" t="inlineStr">
         <is>
-          <t>A 2458-2024</t>
+          <t>A 2461-2024</t>
         </is>
       </c>
       <c r="B868" s="1" t="n">
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52864,7 +52864,7 @@
         </is>
       </c>
       <c r="G868" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="H868" t="n">
         <v>0</v>
@@ -52908,7 +52908,7 @@
         <v>45317</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45317</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45319</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45320</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45322</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53186,14 +53186,14 @@
     <row r="874" ht="15" customHeight="1">
       <c r="A874" t="inlineStr">
         <is>
-          <t>A 4290-2024</t>
+          <t>A 4287-2024</t>
         </is>
       </c>
       <c r="B874" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53206,7 +53206,7 @@
         </is>
       </c>
       <c r="G874" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="H874" t="n">
         <v>0</v>
@@ -53243,14 +53243,14 @@
     <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
-          <t>A 4294-2024</t>
+          <t>A 4290-2024</t>
         </is>
       </c>
       <c r="B875" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53263,7 +53263,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -53300,14 +53300,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 4287-2024</t>
+          <t>A 4294-2024</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53320,7 +53320,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -53364,7 +53364,7 @@
         <v>45328</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         <v>45329</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>45330</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45330</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53585,14 +53585,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 5633-2024</t>
+          <t>A 5605-2024</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53605,7 +53605,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -53642,14 +53642,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 5605-2024</t>
+          <t>A 5633-2024</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -53706,7 +53706,7 @@
         <v>45335</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43332</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43348</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43360</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>43382</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43403</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>43413</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>43418</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>43423</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>43424</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>43426</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>43430</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>43431</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>43453</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>43454</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43473</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43478</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43480</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43481</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43482</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43486</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>43489</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43493</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43502</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43508</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>43509</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>43537</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>43559</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43565</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43567</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43579</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43588</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43612</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>43614</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>43623</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>43626</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>43650</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>43651</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>43696</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>43698</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>43700</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>43706</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>43707</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>43718</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>43719</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>43721</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>43728</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>43732</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>43735</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>43746</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>43755</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>43759</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>43763</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>43767</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>43770</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>43776</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>43777</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>43783</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>43788</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>43790</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>43794</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>43808</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>43809</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>43811</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>43812</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>43818</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43838</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43850</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43852</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>43855</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>43865</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43872</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43873</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>43879</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43888</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43889</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43895</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43896</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43901</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>43906</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>43927</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43936</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>43942</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>43951</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>43955</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43959</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>43962</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>43978</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>43979</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>43980</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>43990</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>43997</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44000</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44005</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44006</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44008</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44011</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44014</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44015</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44022</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>44025</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44026</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44043</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44056</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44060</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>44062</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>44067</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>44068</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44069</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44076</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44078</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44084</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>44095</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44096</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>44098</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44112</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44118</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>44125</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44126</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44127</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44134</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44140</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44144</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44146</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44147</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44152</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44154</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44158</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44160</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44161</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44162</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44175</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44176</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44191</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44192</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44196</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44200</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44204</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44216</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44223</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44228</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44231</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44235</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>44252</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>44258</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>44260</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>44263</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44270</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>44271</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44272</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>44274</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44277</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44278</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44279</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>44281</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44284</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>44286</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44294</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>44295</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>44305</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>44307</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>44308</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>44316</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44319</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>44321</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>44326</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>44333</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44334</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>44336</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44342</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>44343</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>44347</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>44349</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>44350</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44351</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44354</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>44356</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>44361</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>44364</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>44369</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44370</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>44376</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44377</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>44390</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>44414</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>44418</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44419</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>44421</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44427</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44437</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>44438</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44439</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44445</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44446</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>44448</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>44452</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44459</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44461</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>44462</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44466</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44468</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44488</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>44490</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>44491</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44494</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44496</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>44497</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44498</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44502</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44516</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44517</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44518</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44519</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44523</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44526</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>44533</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44538</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44539</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>44543</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>44545</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>44546</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>44546</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44557</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44560</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>44571</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44573</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>44579</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44585</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44586</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>44588</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44589</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44589</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44593</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44599</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44600</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44603</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44603</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>44606</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44606</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44616</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44616</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44628</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44629</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44631</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>44634</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>44635</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44636</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44637</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>44641</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44651</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>44651</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>44655</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>44656</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44658</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44663</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>44663</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44671</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>44671</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44684</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44684</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44691</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44693</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44693</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44694</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>44694</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>44701</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>44706</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44706</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44708</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44713</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44720</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44733</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>44733</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>44734</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44735</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>44735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>44739</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>44741</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>44742</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>44749</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44750</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>44756</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>44756</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44757</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44763</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44767</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44775</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44775</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44776</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44782</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44785</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44785</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44788</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>44790</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>44795</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44796</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44800</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44802</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44804</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44804</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44805</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44805</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>44810</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44810</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44813</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>44813</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44817</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44818</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>44820</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44823</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44823</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>44824</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44827</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44830</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>44840</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>44840</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>44841</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44845</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>44845</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>44846</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>44845</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>44846</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>44848</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>44853</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>44853</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>44859</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>44862</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>44865</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44865</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>44867</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44867</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>44868</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>44869</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>44874</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44876</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44881</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44882</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>44882</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44885</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>44886</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>44886</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>44887</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>44888</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>44889</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>44889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>44895</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44895</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>44896</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44896</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>44897</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>44904</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44904</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44907</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44910</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44910</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44911</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44916</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44922</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44922</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44927</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44928</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44935</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>44935</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44936</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44936</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>44937</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>44937</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>44942</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>44944</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>44946</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44951</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>44959</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44959</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44960</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44962</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44962</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44967</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44970</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44971</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44972</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>44973</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>44973</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>44979</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44979</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44985</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>44985</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>44986</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>44988</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>44991</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>44991</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44992</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>44994</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>44995</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>44999</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45006</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45009</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45012</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45012</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45014</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>45014</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45015</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45015</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45019</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>45019</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45022</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>45022</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45026</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45027</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>45027</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45029</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45029</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45030</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>45030</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>45034</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>45034</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45036</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45036</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45040</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45040</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45044</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45054</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>45054</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45056</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45058</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45069</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45070</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45071</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41371,7 +41371,7 @@
         <v>45071</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45072</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>45072</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45079</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>45082</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>45082</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45084</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>45084</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45085</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>45086</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45086</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45089</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45089</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
         <v>45090</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>45090</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>45096</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45098</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45103</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45104</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>45104</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45106</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>45107</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>45113</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45113</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45120</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45120</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45125</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45133</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45133</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45138</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45138</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45141</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45141</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>45146</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>45146</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>45152</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>45152</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45156</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45156</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45159</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45159</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45161</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>45161</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>45162</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45162</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45168</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45169</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45169</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45176</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45182</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45182</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45184</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45184</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45188</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>45192</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45192</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45194</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45194</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45195</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45196</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45197</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45198</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45203</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46527,7 +46527,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45203</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45204</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45204</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45205</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45208</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45209</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45209</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45211</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45212</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45212</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45217</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45217</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45218</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45218</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45219</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45219</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45220</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45223</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45223</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45224</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45229</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45232</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         <v>45232</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45238</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45239</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45240</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45243</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45243</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45245</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49586,7 +49586,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>45245</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49705,7 +49705,7 @@
         <v>45247</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45250</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49829,7 +49829,7 @@
         <v>45252</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49886,7 +49886,7 @@
         <v>45252</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>45253</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
         <v>45253</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>45255</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>45257</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45257</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>45259</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>45264</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45264</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>45265</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45266</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>45267</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
         <v>45267</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45272</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45272</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>45278</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45278</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>45279</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51668,7 +51668,7 @@
         <v>45282</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51953,7 +51953,7 @@
         <v>45282</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52010,7 +52010,7 @@
         <v>45293</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52067,7 +52067,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52181,7 +52181,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45295</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45300</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45301</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45302</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45302</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45303</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45306</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>45308</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45308</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>45312</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45312</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52987,14 +52987,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 3337-2024</t>
+          <t>A 3334-2024</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -53044,14 +53044,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 3334-2024</t>
+          <t>A 3337-2024</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -53108,7 +53108,7 @@
         <v>45319</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>45320</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53222,7 +53222,7 @@
         <v>45322</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53272,14 +53272,14 @@
     <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
-          <t>A 4287-2024</t>
+          <t>A 4290-2024</t>
         </is>
       </c>
       <c r="B875" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53292,7 +53292,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -53329,14 +53329,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 4290-2024</t>
+          <t>A 4294-2024</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -53386,14 +53386,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 4294-2024</t>
+          <t>A 4287-2024</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -53450,7 +53450,7 @@
         <v>45328</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53507,7 +53507,7 @@
         <v>45329</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>45330</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
         <v>45330</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53678,7 +53678,7 @@
         <v>45334</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53735,7 +53735,7 @@
         <v>45334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53792,7 +53792,7 @@
         <v>45335</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53849,7 +53849,7 @@
         <v>45338</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43332</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43348</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43360</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>43382</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43403</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>43413</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>43418</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>43423</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>43424</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>43426</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>43430</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>43431</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>43453</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>43454</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43473</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43478</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43480</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43481</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43482</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43486</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>43489</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43493</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43502</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43508</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>43509</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>43537</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>43559</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43565</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43567</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43579</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43588</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43612</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>43614</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>43623</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>43626</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>43650</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>43651</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>43696</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>43698</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>43700</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>43706</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>43707</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>43718</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>43719</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>43721</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>43728</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>43732</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>43735</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>43746</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>43755</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>43759</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>43763</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>43767</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>43770</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>43776</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>43777</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>43783</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>43788</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>43790</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>43794</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>43808</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>43809</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>43811</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>43812</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>43818</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43838</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43850</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43852</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>43855</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>43865</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43872</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43873</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>43879</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43888</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43889</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43895</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43896</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43901</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>43906</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>43927</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43936</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>43942</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>43951</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>43955</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43959</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>43962</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>43978</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>43979</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>43980</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>43990</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>43997</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44000</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44005</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44006</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44008</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44011</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44014</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44015</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44022</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>44025</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44026</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44043</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44056</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44060</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>44062</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>44067</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>44068</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44069</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44076</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44078</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44084</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>44095</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44096</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>44098</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44112</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44118</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>44125</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44126</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44127</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44134</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44140</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44144</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44146</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44147</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44152</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44154</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44158</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44160</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44161</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44162</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44175</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44176</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44191</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44192</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44196</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44200</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44204</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44216</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44223</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44228</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44231</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44235</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>44252</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>44258</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>44260</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>44263</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44270</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>44271</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44272</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>44274</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44277</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44278</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44279</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>44281</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44284</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>44286</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44294</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>44295</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>44305</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>44307</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>44308</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>44316</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44319</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>44321</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>44326</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>44333</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44334</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>44336</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44342</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>44343</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>44347</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>44349</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>44350</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44351</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44354</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>44356</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>44361</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>44364</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>44369</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44370</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>44376</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44377</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>44390</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>44414</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>44418</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44419</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>44421</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44427</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44437</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>44438</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44439</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44445</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44446</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>44448</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>44452</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44459</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44461</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>44462</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44466</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44468</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44488</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>44490</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>44491</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44494</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44496</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>44497</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44498</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44502</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44516</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44517</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44518</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44519</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44523</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44526</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>44533</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44538</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44539</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>44543</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>44545</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>44546</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>44546</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44557</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44560</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>44571</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44573</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>44579</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44585</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44586</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>44588</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44589</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44589</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44593</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44599</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44600</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44603</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44603</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>44606</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44606</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44616</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44616</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44628</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44629</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44631</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>44634</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>44635</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44636</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44637</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>44641</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44651</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>44651</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>44655</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>44656</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44658</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44663</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>44663</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44671</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>44671</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44684</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44684</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44691</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44693</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44693</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44694</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>44694</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>44701</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>44706</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44706</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44708</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44713</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44720</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44733</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>44733</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>44734</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44735</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>44735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>44739</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>44741</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>44742</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>44749</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44750</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>44756</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>44756</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44757</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44763</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44767</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44775</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44775</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44776</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44782</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44785</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44785</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44788</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>44790</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>44795</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44796</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44800</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44802</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44804</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44804</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44805</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44805</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>44810</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44810</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44813</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>44813</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44817</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44818</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>44820</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44823</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44823</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>44824</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44827</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44830</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>44840</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>44840</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>44841</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44845</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>44845</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>44846</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>44845</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>44846</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>44848</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>44853</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>44853</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>44859</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>44862</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>44865</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44865</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>44867</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44867</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>44868</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>44869</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>44874</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44876</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44881</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44882</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>44882</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44885</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>44886</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>44886</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>44887</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>44888</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>44889</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>44889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>44895</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44895</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>44896</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44896</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>44897</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>44904</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44904</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44907</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44910</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44910</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44911</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44916</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44922</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44922</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44927</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44928</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44935</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>44935</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44936</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44936</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>44937</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>44937</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>44942</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>44944</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>44946</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44951</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>44959</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44959</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44960</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44962</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44962</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44967</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44970</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44971</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44972</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>44973</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>44973</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>44979</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44979</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44985</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>44985</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>44986</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>44988</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>44991</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>44991</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44992</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>44994</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>44995</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>44999</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45006</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45009</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45012</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45012</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45014</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>45014</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45015</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45015</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45019</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>45019</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45022</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>45022</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45026</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45027</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>45027</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45029</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45029</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45030</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>45030</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>45034</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>45034</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45036</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45036</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45040</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45040</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45044</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45054</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>45054</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45056</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45058</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45069</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45070</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45071</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41371,7 +41371,7 @@
         <v>45071</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45072</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>45072</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45079</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>45082</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>45082</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45084</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>45084</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45085</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>45086</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45086</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45089</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45089</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
         <v>45090</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>45090</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>45096</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45098</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45103</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45104</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>45104</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45106</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>45107</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>45113</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45113</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45120</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45120</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45125</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45133</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45133</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45138</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45138</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45141</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45141</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>45146</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>45146</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>45152</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>45152</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45156</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45156</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45159</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45159</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45161</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>45161</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>45162</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45162</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45168</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45169</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45169</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45176</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45182</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45182</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45184</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45184</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45188</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>45192</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45192</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45194</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45194</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45195</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45196</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45197</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45198</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45203</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46527,7 +46527,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45203</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45204</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45204</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45205</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45208</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45209</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45209</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45211</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45212</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45212</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45217</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45217</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45218</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45218</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45219</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45219</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45220</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45223</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45223</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45224</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45229</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45232</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         <v>45232</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45238</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45239</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45240</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45243</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45243</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45245</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49586,7 +49586,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>45245</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49705,7 +49705,7 @@
         <v>45247</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45250</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49829,7 +49829,7 @@
         <v>45252</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49886,7 +49886,7 @@
         <v>45252</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>45253</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
         <v>45253</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>45255</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>45257</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45257</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>45259</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>45264</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45264</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>45265</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45266</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>45267</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
         <v>45267</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45272</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45272</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>45278</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45278</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>45279</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51668,7 +51668,7 @@
         <v>45282</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51953,7 +51953,7 @@
         <v>45282</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52010,7 +52010,7 @@
         <v>45293</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52067,7 +52067,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52181,7 +52181,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45295</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45300</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45301</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45302</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45302</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45303</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45306</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>45308</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45308</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>45312</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45312</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52987,14 +52987,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 3334-2024</t>
+          <t>A 3337-2024</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -53044,14 +53044,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 3337-2024</t>
+          <t>A 3334-2024</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -53108,7 +53108,7 @@
         <v>45319</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>45320</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53222,7 +53222,7 @@
         <v>45322</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53272,14 +53272,14 @@
     <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
-          <t>A 4290-2024</t>
+          <t>A 4287-2024</t>
         </is>
       </c>
       <c r="B875" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53292,7 +53292,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -53329,14 +53329,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 4294-2024</t>
+          <t>A 4290-2024</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -53386,14 +53386,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 4287-2024</t>
+          <t>A 4294-2024</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -53450,7 +53450,7 @@
         <v>45328</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53507,7 +53507,7 @@
         <v>45329</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>45330</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
         <v>45330</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53671,14 +53671,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 5633-2024</t>
+          <t>A 5605-2024</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -53728,14 +53728,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 5605-2024</t>
+          <t>A 5633-2024</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -53792,7 +53792,7 @@
         <v>45335</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53849,7 +53849,7 @@
         <v>45338</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>43332</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>43348</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>43360</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>43382</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43403</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>43411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>43413</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>43418</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>43423</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>43424</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>43426</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>43430</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>43431</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>43440</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>43447</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>43453</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>43454</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>43473</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>43476</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>43478</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>43479</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>43480</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>43481</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>43482</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>43486</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>43489</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>43493</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>43495</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>43502</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>43508</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>43509</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>43510</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>43511</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>43537</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>43559</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>43565</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>43567</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43579</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43588</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>43612</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>43614</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>43623</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>43626</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>43650</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>43651</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>43696</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>43698</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>43700</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>43706</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>43707</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>43718</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>43719</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>43721</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>43728</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>43732</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>43735</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>43746</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>43755</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>43759</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>43761</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>43763</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>43767</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>43770</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>43776</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>43777</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>43783</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>43788</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>43790</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>43794</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>43808</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>43809</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>43811</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>43812</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>43818</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>43838</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>43850</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>43852</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>43854</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>43855</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>43865</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>43871</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>43872</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>43873</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>43879</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>43888</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>43889</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>43895</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>43896</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>43901</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>43906</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>43927</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>43936</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>43942</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>43951</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>43955</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>43959</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>43962</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>43978</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>43979</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>43980</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>43990</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>43997</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44000</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>44005</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44006</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44008</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44011</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44014</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>44015</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44022</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>44025</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44026</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44043</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44056</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>44060</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>44062</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>44067</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>44068</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>44069</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44076</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44078</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44084</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>44095</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44096</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>44098</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44109</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44112</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44118</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>44125</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44126</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44127</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44134</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44140</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44144</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44146</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44147</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44152</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44154</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44158</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44160</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44161</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44162</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44175</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44176</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44191</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44192</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44196</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44200</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44204</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44216</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44223</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44228</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44231</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>44235</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>44252</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>44258</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>44260</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>44263</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44270</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>44271</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44272</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>44274</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>44277</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44278</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44279</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>44281</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44284</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>44286</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44294</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>44295</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44300</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>44305</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>44307</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>44308</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>44316</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44319</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>44321</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>44326</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>44333</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44334</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>44336</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>44342</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>44343</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>44347</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>44349</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>44350</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44351</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44354</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>44356</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>44361</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>44364</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>44369</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>44370</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>44376</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44377</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>44389</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>44390</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>44414</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>44418</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44419</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>44421</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44427</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44437</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>44438</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44439</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44445</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44446</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>44448</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>44452</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>44455</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44459</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44461</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>44462</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>44466</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44468</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44473</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44488</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>44490</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>44491</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
         <v>44494</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>44496</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>44497</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>44498</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44502</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>44516</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44517</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44518</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44519</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44523</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44526</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>44533</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44538</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44539</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>44543</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>44545</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>44546</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>44546</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44557</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>44560</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>44571</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44573</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>44579</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>44580</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44585</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>44586</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44586</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>44588</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>44589</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>44589</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44593</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>44594</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44599</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>44600</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44603</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44603</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>44606</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44606</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>44616</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>44616</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44628</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44629</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>44629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44631</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>44634</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>44635</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44636</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44637</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>44641</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>44651</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>44651</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>44655</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>44656</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44658</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44663</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>44663</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44671</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>44671</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44684</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44684</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44691</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44693</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44693</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44694</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>44694</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>44701</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>44706</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28750,7 +28750,7 @@
         <v>44706</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>44708</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44713</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44720</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>44733</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>44733</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>44734</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44735</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>44735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>44739</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>44741</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>44742</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>44749</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44750</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>44756</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>44756</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30101,7 +30101,7 @@
         <v>44757</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44763</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30215,7 +30215,7 @@
         <v>44767</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>44775</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44775</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>44776</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44782</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44785</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>44785</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44788</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>44790</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>44795</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44796</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>44800</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>44802</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44804</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>44804</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44805</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>44805</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>44810</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44810</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>44813</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>44813</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>44817</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44818</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>44820</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31757,7 +31757,7 @@
         <v>44823</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44823</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>44824</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>44827</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44830</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>44840</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>44840</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>44841</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>44845</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>44845</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>44846</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>44845</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>44846</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>44848</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>44853</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>44853</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>44859</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>44862</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>44865</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44865</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>44867</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44867</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>44868</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>44869</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>44874</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33237,7 +33237,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>44876</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44876</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44881</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>44882</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>44882</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>44885</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>44886</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>44886</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33993,7 +33993,7 @@
         <v>44887</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>44888</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>44889</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>44889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>44895</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>44895</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>44896</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44896</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>44897</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>44904</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44904</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44907</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>44910</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>44910</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>44911</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44916</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>44922</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>44922</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44927</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44928</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>44935</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35597,7 +35597,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>44935</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44936</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>44936</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>44937</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>44937</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>44942</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>44943</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>44944</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>44946</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>44951</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>44959</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44959</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44960</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44962</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44962</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44967</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44970</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44971</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44972</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>44973</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>44973</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>44979</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44979</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>44985</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>44985</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>44986</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>44988</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>44991</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>44991</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>44992</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>44994</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>44995</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38609,7 +38609,7 @@
         <v>44999</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45006</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45009</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45012</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45012</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         <v>45014</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         <v>45014</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45015</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45015</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39452,7 +39452,7 @@
         <v>45019</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39566,7 +39566,7 @@
         <v>45019</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45022</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39747,7 +39747,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>45022</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45026</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45027</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>45027</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45029</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>45029</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45030</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40352,7 +40352,7 @@
         <v>45030</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>45034</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>45034</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45036</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45036</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45040</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45040</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45044</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45054</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>45054</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45056</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45058</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>45069</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41252,7 +41252,7 @@
         <v>45070</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>45071</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41371,7 +41371,7 @@
         <v>45071</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45072</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>45072</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41552,7 +41552,7 @@
         <v>45079</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>45082</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>45082</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>45084</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>45084</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45085</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>45086</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45086</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45089</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42189,7 +42189,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45089</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
         <v>45090</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>45090</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>45096</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45098</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45103</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45104</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>45104</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45106</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>45107</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>45113</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45113</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45117</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45120</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45120</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45125</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45133</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45133</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45138</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45138</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45141</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45141</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>45146</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>45146</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>45152</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>45152</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45156</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45156</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44477,7 +44477,7 @@
         <v>45159</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45159</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44705,7 +44705,7 @@
         <v>45161</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>45161</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>45162</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45162</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45168</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45169</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>45169</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45176</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45414,7 +45414,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>45182</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45533,7 +45533,7 @@
         <v>45182</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45184</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>45184</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45188</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>45192</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45192</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45194</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45194</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45195</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46113,7 +46113,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>45196</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45197</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45198</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45203</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46527,7 +46527,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45203</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45204</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45204</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45205</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45208</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45209</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45209</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45211</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45212</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>45212</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45217</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45217</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45218</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45218</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45219</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45219</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45220</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45223</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45223</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45224</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45229</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>45231</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45232</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48587,7 +48587,7 @@
         <v>45232</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45238</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45239</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45240</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45243</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48877,7 +48877,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48991,7 +48991,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49048,7 +49048,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45243</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45245</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49586,7 +49586,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>45245</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49705,7 +49705,7 @@
         <v>45247</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45250</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49829,7 +49829,7 @@
         <v>45252</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49886,7 +49886,7 @@
         <v>45252</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>45253</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
         <v>45253</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>45255</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>45257</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50409,7 +50409,7 @@
         <v>45257</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>45259</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45261</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>45264</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45264</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>45265</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50870,7 +50870,7 @@
         <v>45266</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50984,7 +50984,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51098,7 +51098,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>45267</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
         <v>45267</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45272</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>45272</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>45278</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>45278</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>45279</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51668,7 +51668,7 @@
         <v>45282</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51953,7 +51953,7 @@
         <v>45282</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52010,7 +52010,7 @@
         <v>45293</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52067,7 +52067,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52181,7 +52181,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45295</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45300</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45301</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45302</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45302</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45303</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45306</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>45308</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45308</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52823,7 +52823,7 @@
         <v>45312</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45312</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>45317</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45317</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>45319</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>45320</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53222,7 +53222,7 @@
         <v>45322</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53272,14 +53272,14 @@
     <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
-          <t>A 4287-2024</t>
+          <t>A 4290-2024</t>
         </is>
       </c>
       <c r="B875" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53292,7 +53292,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -53329,14 +53329,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 4290-2024</t>
+          <t>A 4294-2024</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -53386,14 +53386,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 4294-2024</t>
+          <t>A 4287-2024</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -53450,7 +53450,7 @@
         <v>45328</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53507,7 +53507,7 @@
         <v>45329</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>45330</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
         <v>45330</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53671,14 +53671,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 5605-2024</t>
+          <t>A 5633-2024</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -53728,14 +53728,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 5633-2024</t>
+          <t>A 5605-2024</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -53792,7 +53792,7 @@
         <v>45335</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53849,7 +53849,7 @@
         <v>45338</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45344</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>43332</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>43348</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>43360</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43382</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43403</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>43411</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>43413</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>43424</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>43426</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>43430</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>43447</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>43453</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43478</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>43489</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>43493</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>43502</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>43508</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>43509</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>43510</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43511</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>43530</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>43537</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43559</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43565</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43567</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43579</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43588</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>43612</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>43614</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43623</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>43626</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43635</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43650</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43651</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43706</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>43718</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43721</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43732</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43755</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43759</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43761</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43763</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43767</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43770</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43776</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43777</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43783</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43788</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>43790</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43794</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43809</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43811</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>43812</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43818</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>43838</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>43850</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43852</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>43854</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>43855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>43865</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>43871</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>43872</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>43873</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>43879</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>43895</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>43896</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>43901</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>43906</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>43927</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>43936</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>43942</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>43951</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43955</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>43959</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43962</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>43978</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43979</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43980</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43990</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43997</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44000</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44005</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44006</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44008</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44011</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44014</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44015</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44022</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44025</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44026</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44043</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44056</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44060</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44062</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>44067</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44078</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44081</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44084</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44095</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44096</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44098</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>44109</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44112</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44118</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44126</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44127</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44134</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44140</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44144</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44146</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44147</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44152</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44154</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44158</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44161</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44162</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44175</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44176</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>44191</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44192</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44196</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44200</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44204</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44216</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44228</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44231</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44235</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44252</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44258</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44260</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44263</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44270</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44271</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44272</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44274</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44277</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>44278</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44279</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44281</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44284</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44286</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44294</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44295</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44300</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44305</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44307</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44308</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44319</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44321</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44326</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44333</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44334</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44336</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44342</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44343</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44347</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44349</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44350</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44351</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44354</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44356</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44361</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44364</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>44369</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44370</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44376</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44377</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44390</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44414</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44418</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44419</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44421</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44427</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>44437</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44438</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44439</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44446</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44448</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44452</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44459</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44461</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44468</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44473</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44488</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44490</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44491</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44494</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44496</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44497</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44498</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44502</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44516</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44517</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44523</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44526</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44533</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44538</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44539</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44543</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44545</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>44546</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44546</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44557</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44560</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>44571</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44573</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>44579</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44585</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44586</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44586</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44588</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44589</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44589</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44599</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44600</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44603</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44603</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44606</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44606</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44616</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44616</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44628</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44629</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44631</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>44634</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44635</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44636</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44637</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44641</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44651</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44651</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44655</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44656</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44658</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44663</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>44663</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44671</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44671</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44684</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44684</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>44691</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>44693</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44693</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44694</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44694</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44701</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44706</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44706</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>44708</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>44713</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44720</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44733</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44733</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44734</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>44735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44735</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>44739</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>44741</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44749</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44750</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44756</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44756</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44757</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44763</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44767</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44775</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>44775</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>44776</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44782</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44785</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44785</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44788</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44790</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44795</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44796</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>44800</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44802</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44804</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44804</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44805</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44805</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44810</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44810</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44813</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44813</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44817</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>44818</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>44820</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44823</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44823</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44824</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44827</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44830</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>44840</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>44840</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44841</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44845</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44845</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44846</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44845</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44846</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44848</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44853</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>44853</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>44859</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>44862</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>44865</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44865</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44867</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44867</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>44868</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44869</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>44874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44874</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44876</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44876</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44881</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44882</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>44882</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>44885</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44886</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>44886</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>44887</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44888</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>44889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>44895</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44895</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>44896</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44896</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>44897</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44904</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>44904</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44907</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>44910</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>44910</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>44911</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>44916</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>44922</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>44922</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>44927</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>44935</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>44935</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>44936</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>44936</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44937</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44937</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>44942</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44943</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44944</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44946</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>44951</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44959</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44959</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44960</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44962</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44962</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44967</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44970</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44971</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44972</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>44973</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>44973</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44979</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44979</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44985</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>44985</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44986</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44988</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44991</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44991</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>44992</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44994</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44995</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44999</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45006</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45009</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45012</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45012</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45014</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45014</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45015</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45015</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45019</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45019</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45022</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45026</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45027</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45027</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45029</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45029</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45030</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45030</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45034</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45034</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45036</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45036</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45040</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45040</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45054</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45054</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45056</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45058</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45069</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45070</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45071</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45071</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45072</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45072</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45079</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45082</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45082</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45084</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45084</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45085</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45086</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45086</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45089</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45089</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45090</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45090</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45096</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45098</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>45103</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45104</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45104</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45106</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45107</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45113</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45113</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45117</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45120</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45120</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45125</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45133</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45133</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45138</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45138</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45141</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45141</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45146</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45146</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45152</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45152</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45156</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45156</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45159</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45159</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45161</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45161</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45162</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45162</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45168</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45169</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45169</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45182</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45184</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45184</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45188</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45192</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45192</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>45194</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45194</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45195</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45196</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45197</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45198</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45203</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45203</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>45204</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45204</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45205</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45208</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45209</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45209</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45211</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45212</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45212</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45217</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45217</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45218</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45218</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45219</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45219</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45220</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45223</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45223</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45224</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45229</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>45229</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45232</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45232</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45238</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45239</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45240</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45243</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45243</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45245</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45245</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45247</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45250</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45252</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45252</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45253</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45253</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45255</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45257</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45257</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45259</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45264</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45265</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45267</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45267</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45272</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45272</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45278</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45278</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45279</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45282</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45282</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45293</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45295</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45300</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45301</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45302</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>45302</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45303</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52737,7 +52737,7 @@
         <v>45306</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45308</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45308</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45312</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45312</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45317</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45317</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45319</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45320</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45322</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53357,14 +53357,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 4287-2024</t>
+          <t>A 4290-2024</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53377,7 +53377,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -53414,14 +53414,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 4290-2024</t>
+          <t>A 4294-2024</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53434,7 +53434,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -53471,14 +53471,14 @@
     <row r="878" ht="15" customHeight="1">
       <c r="A878" t="inlineStr">
         <is>
-          <t>A 4294-2024</t>
+          <t>A 4287-2024</t>
         </is>
       </c>
       <c r="B878" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53491,7 +53491,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -53535,7 +53535,7 @@
         <v>45328</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45329</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53642,14 +53642,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 5243-2024</t>
+          <t>A 5241-2024</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -53699,14 +53699,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 5241-2024</t>
+          <t>A 5243-2024</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53719,7 +53719,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -53756,14 +53756,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 5605-2024</t>
+          <t>A 5633-2024</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -53813,14 +53813,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 5633-2024</t>
+          <t>A 5605-2024</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -53877,7 +53877,7 @@
         <v>45335</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45338</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53984,14 +53984,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 7297-2024</t>
+          <t>A 7298-2024</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="H887" t="n">
         <v>0</v>
@@ -54041,14 +54041,14 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>A 7298-2024</t>
+          <t>A 7297-2024</t>
         </is>
       </c>
       <c r="B888" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45344</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>43332</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>43348</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>43360</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43382</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43403</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>43411</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>43413</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>43424</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>43426</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>43430</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>43447</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>43453</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43478</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>43489</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>43493</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>43502</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>43508</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>43509</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>43510</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43511</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>43530</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>43537</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43559</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43565</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43567</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43579</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43588</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>43612</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>43614</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43623</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>43626</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43635</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43650</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43651</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43706</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>43718</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43721</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43732</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43755</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43759</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43761</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43763</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43767</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43770</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43776</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43777</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43783</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43788</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>43790</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43794</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43809</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43811</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>43812</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43818</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>43838</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>43850</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43852</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>43854</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>43855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>43865</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>43871</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>43872</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>43873</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>43879</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>43895</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>43896</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>43901</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>43906</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>43927</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>43936</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>43942</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>43951</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43955</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>43959</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43962</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>43978</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43979</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43980</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43990</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43997</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44000</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44005</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44006</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44008</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44011</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44014</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44015</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44022</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44025</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44026</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44043</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44056</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44060</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44062</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>44067</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44078</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44081</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44084</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44095</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44096</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44098</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>44109</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44112</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44118</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44126</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44127</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44134</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44140</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44144</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44146</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44147</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44152</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44154</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44158</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44161</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44162</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44175</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44176</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>44191</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44192</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44196</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44200</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44204</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44216</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44228</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44231</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44235</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44252</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44258</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44260</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44263</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44270</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44271</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44272</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44274</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44277</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>44278</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44279</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44281</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44284</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44286</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44294</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44295</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44300</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44305</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44307</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44308</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44319</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44321</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44326</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44333</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44334</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44336</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44342</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44343</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44347</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44349</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44350</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44351</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44354</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44356</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44361</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44364</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>44369</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44370</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44376</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44377</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44390</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44414</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44418</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44419</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44421</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44427</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>44437</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44438</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44439</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44446</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44448</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44452</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44459</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44461</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44468</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44473</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44488</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44490</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44491</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44494</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44496</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44497</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44498</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44502</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44516</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44517</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44523</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44526</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44533</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44538</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44539</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44543</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44545</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>44546</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44546</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44557</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44560</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>44571</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44573</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>44579</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44585</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44586</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44586</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44588</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44589</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44589</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44599</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44600</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44603</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44603</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44606</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44606</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44616</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44616</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44628</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44629</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44631</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>44634</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44635</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44636</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44637</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44641</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44651</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44651</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44655</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44656</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44658</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44663</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>44663</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44671</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44671</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44684</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44684</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>44691</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>44693</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44693</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44694</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44694</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44701</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44706</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44706</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>44708</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>44713</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44720</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44733</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44733</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44734</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>44735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44735</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>44739</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>44741</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44749</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44750</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44756</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44756</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44757</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44763</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44767</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44775</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>44775</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>44776</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44782</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44785</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44785</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44788</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44790</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44795</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44796</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>44800</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44802</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44804</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44804</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44805</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44805</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44810</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44810</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44813</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44813</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44817</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>44818</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>44820</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44823</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44823</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44824</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44827</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44830</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>44840</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>44840</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44841</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44845</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44845</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44846</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44845</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44846</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44848</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44853</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>44853</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>44859</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>44862</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>44865</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44865</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44867</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44867</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>44868</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44869</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>44874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44874</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44876</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44876</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44881</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44882</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>44882</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>44885</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44886</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>44886</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>44887</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44888</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>44889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>44895</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44895</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>44896</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44896</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>44897</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44904</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>44904</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44907</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>44910</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>44910</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>44911</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>44916</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>44922</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>44922</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>44927</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>44935</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>44935</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>44936</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>44936</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44937</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44937</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>44942</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44943</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44944</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44946</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>44951</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44959</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44959</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44960</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44962</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44962</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44967</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44970</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44971</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44972</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>44973</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>44973</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44979</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44979</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44985</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>44985</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44986</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44988</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44991</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44991</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>44992</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44994</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44995</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44999</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45006</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45009</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45012</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45012</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45014</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45014</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45015</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45015</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45019</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45019</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45022</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45026</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45027</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45027</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45029</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45029</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45030</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45030</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45034</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45034</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45036</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45036</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45040</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45040</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45054</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45054</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45056</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45058</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45069</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45070</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45071</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45071</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45072</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45072</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45079</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45082</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45082</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45084</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45084</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45085</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45086</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45086</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45089</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45089</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45090</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45090</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45096</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45098</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>45103</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45104</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45104</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45106</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45107</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45113</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45113</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45117</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45120</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45120</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45125</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45133</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45133</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45138</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45138</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45141</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45141</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45146</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45146</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45152</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45152</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45156</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45156</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45159</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45159</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45161</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45161</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45162</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45162</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45168</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45169</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45169</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45182</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45184</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45184</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45188</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45192</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45192</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>45194</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45194</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45195</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45196</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45197</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45198</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45203</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45203</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>45204</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45204</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45205</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45208</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45209</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45209</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45211</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45212</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45212</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45217</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45217</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45218</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45218</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45219</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45219</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45220</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45223</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45223</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45224</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45229</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>45229</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45232</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45232</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45238</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45239</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45240</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45243</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45243</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45245</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45245</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45247</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45250</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45252</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45252</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45253</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45253</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45255</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45257</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45257</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45259</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45264</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45265</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45267</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45267</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45272</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45272</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45278</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45278</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45279</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45282</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45282</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45293</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45295</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45300</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45301</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45302</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>45302</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45303</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52737,7 +52737,7 @@
         <v>45306</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45308</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45308</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45312</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45312</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45317</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45317</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45319</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45320</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45322</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         <v>45324</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>45324</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45328</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45329</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53642,14 +53642,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 5241-2024</t>
+          <t>A 5243-2024</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -53699,14 +53699,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 5243-2024</t>
+          <t>A 5241-2024</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53719,7 +53719,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -53763,7 +53763,7 @@
         <v>45334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         <v>45334</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45335</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45338</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45344</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45344</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45344</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>43332</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>43348</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>43360</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43382</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43403</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>43411</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>43413</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>43424</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>43426</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>43430</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>43447</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>43453</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43478</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>43489</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>43493</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>43502</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>43508</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>43509</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>43510</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43511</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>43530</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>43537</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43559</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43565</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43567</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43579</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43588</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>43612</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>43614</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43623</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>43626</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43635</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43650</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43651</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43706</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>43718</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43721</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43732</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43755</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43759</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43761</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43763</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43767</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43770</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43776</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43777</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43783</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43788</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>43790</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43794</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43809</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43811</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>43812</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43818</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>43838</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>43850</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43852</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>43854</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>43855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>43865</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>43871</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>43872</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>43873</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>43879</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>43895</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>43896</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>43901</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>43906</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>43927</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>43936</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>43942</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>43951</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43955</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>43959</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43962</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>43978</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43979</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43980</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43990</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43997</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44000</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44005</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44006</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44008</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44011</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44014</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44015</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44022</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44025</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44026</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44043</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44056</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44060</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44062</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>44067</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44078</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44081</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44084</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44095</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44096</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44098</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>44109</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44112</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44118</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44126</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44127</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44134</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44140</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44144</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44146</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44147</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44152</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44154</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44158</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44161</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44162</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44175</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44176</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>44191</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44192</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44196</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44200</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44204</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44216</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44228</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44231</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44235</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44252</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44258</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44260</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44263</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44270</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44271</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44272</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44274</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44277</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>44278</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44279</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44281</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44284</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44286</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44294</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44295</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44300</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44305</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44307</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44308</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44319</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44321</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44326</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44333</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44334</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44336</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44342</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44343</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44347</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44349</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44350</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44351</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44354</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44356</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44361</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44364</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>44369</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44370</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44376</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44377</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44390</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44414</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44418</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44419</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44421</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44427</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>44437</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44438</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44439</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44446</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44448</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44452</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44459</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44461</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44468</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44473</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44488</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44490</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44491</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44494</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44496</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44497</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44498</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44502</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44516</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44517</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44523</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44526</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44533</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44538</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44539</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44543</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44545</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>44546</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44546</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44557</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44560</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>44571</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44573</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>44579</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44585</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44586</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44586</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44588</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44589</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44589</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44599</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44600</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44603</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44603</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44606</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44606</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44616</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44616</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44628</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44629</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44631</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>44634</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44635</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44636</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44637</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44641</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44651</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44651</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44655</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44656</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44658</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44663</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>44663</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44671</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44671</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44684</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44684</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>44691</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>44693</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44693</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44694</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44694</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44701</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44706</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44706</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>44708</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>44713</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44720</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44733</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44733</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44734</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>44735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44735</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>44739</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>44741</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44749</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44750</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44756</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44756</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44757</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44763</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44767</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44775</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>44775</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>44776</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44782</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44785</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44785</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44788</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44790</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44795</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44796</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>44800</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44802</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44804</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44804</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44805</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44805</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44810</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44810</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44813</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44813</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44817</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>44818</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>44820</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44823</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44823</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44824</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44827</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44830</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>44840</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>44840</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44841</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44845</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44845</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44846</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44845</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44846</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44848</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44853</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>44853</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>44859</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>44862</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>44865</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44865</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44867</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44867</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>44868</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44869</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>44874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44874</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44876</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44876</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44881</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44882</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>44882</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>44885</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44886</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>44886</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>44887</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44888</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>44889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>44895</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44895</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>44896</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44896</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>44897</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44904</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>44904</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44907</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>44910</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>44910</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>44911</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>44916</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>44922</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>44922</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>44927</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>44935</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>44935</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>44936</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>44936</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44937</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44937</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>44942</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44943</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44944</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44946</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>44951</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44959</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44959</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44960</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44962</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44962</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44967</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44970</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44971</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44972</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>44973</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>44973</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44979</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44979</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44985</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>44985</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44986</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44988</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44991</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44991</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>44992</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44994</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44995</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44999</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45006</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45009</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45012</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45012</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45014</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45014</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45015</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45015</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45019</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45019</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45022</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45026</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45027</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45027</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45029</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45029</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45030</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45030</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45034</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45034</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45036</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45036</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45040</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45040</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45054</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45054</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45056</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45058</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45069</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45070</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45071</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45071</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45072</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45072</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45079</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45082</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45082</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45084</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45084</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45085</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45086</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45086</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45089</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45089</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45090</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45090</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45096</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45098</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>45103</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45104</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45104</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45106</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45107</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45113</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45113</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45117</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45120</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45120</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45125</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45133</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45133</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45138</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45138</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45141</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45141</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45146</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45146</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45152</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45152</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45156</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45156</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45159</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45159</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45161</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45161</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45162</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45162</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45168</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45169</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45169</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45182</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45184</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45184</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45188</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45192</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45192</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>45194</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45194</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45195</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45196</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45197</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45198</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45203</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45203</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>45204</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45204</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45205</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45208</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45209</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45209</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45211</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45212</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45212</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45217</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45217</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45218</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45218</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45219</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45219</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45220</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45223</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45223</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45224</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45229</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>45229</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45232</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45232</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45238</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45239</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45240</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45243</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45243</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45245</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45245</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45247</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45250</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45252</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45252</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45253</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45253</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45255</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45257</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45257</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45259</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45264</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45265</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45267</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45267</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45272</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45272</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45278</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45278</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45279</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45282</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45282</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45293</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45295</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45300</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45301</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45302</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>45302</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45303</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52737,7 +52737,7 @@
         <v>45306</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45308</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45308</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45312</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45312</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45317</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45317</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45319</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45320</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45322</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53357,14 +53357,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 4290-2024</t>
+          <t>A 4287-2024</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53377,7 +53377,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -53414,14 +53414,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 4294-2024</t>
+          <t>A 4290-2024</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53434,7 +53434,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -53471,14 +53471,14 @@
     <row r="878" ht="15" customHeight="1">
       <c r="A878" t="inlineStr">
         <is>
-          <t>A 4287-2024</t>
+          <t>A 4294-2024</t>
         </is>
       </c>
       <c r="B878" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53491,7 +53491,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -53535,7 +53535,7 @@
         <v>45328</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45329</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53642,14 +53642,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 5243-2024</t>
+          <t>A 5241-2024</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53662,7 +53662,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -53699,14 +53699,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 5241-2024</t>
+          <t>A 5243-2024</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53719,7 +53719,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -53756,14 +53756,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 5633-2024</t>
+          <t>A 5605-2024</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -53813,14 +53813,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 5605-2024</t>
+          <t>A 5633-2024</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -53877,7 +53877,7 @@
         <v>45335</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45338</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53984,14 +53984,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 7298-2024</t>
+          <t>A 7297-2024</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="H887" t="n">
         <v>0</v>
@@ -54041,14 +54041,14 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>A 7297-2024</t>
+          <t>A 7298-2024</t>
         </is>
       </c>
       <c r="B888" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45344</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>43332</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>43348</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>43360</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43382</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43403</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>43411</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>43413</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>43424</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>43426</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>43430</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>43447</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>43453</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43478</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>43489</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>43493</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>43502</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>43508</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>43509</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>43510</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43511</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>43530</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>43537</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43559</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43565</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43567</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43579</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43588</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>43612</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>43614</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43623</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>43626</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43635</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43650</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43651</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43706</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>43718</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43721</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43732</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43755</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43759</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43761</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43763</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43767</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43770</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43776</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43777</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43783</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43788</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>43790</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43794</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43809</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43811</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>43812</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43818</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>43838</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>43850</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43852</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>43854</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>43855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>43865</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>43871</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>43872</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>43873</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>43879</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>43895</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>43896</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>43901</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>43906</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>43927</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>43936</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>43942</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>43951</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43955</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>43959</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43962</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>43978</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43979</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43980</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43990</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43997</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44000</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44005</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44006</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44008</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44011</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44014</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44015</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44022</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44025</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44026</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44043</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44056</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44060</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44062</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>44067</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44078</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44081</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44084</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44095</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44096</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44098</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>44109</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44112</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44118</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44126</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44127</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44134</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44140</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44144</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44146</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44147</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44152</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44154</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44158</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44161</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44162</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44175</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44176</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>44191</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44192</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44196</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44200</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44204</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44216</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44228</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44231</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44235</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44252</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44258</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44260</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44263</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44270</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44271</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44272</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44274</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44277</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>44278</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44279</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44281</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44284</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44286</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44294</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44295</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44300</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44305</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44307</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44308</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44319</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44321</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44326</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44333</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44334</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44336</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44342</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44343</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44347</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44349</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44350</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44351</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44354</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44356</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44361</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44364</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>44369</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44370</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44376</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44377</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44390</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44414</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44418</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44419</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44421</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44427</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>44437</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44438</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44439</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44446</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44448</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44452</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44459</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44461</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44468</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44473</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44488</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44490</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44491</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44494</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44496</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44497</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44498</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44502</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44516</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44517</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44523</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44526</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44533</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44538</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44539</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44543</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44545</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>44546</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44546</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44557</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44560</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>44571</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44573</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>44579</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44585</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44586</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44586</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44588</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44589</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44589</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44599</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44600</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44603</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44603</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44606</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44606</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44616</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44616</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44628</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44629</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44631</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>44634</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44635</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44636</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44637</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44641</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44651</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44651</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44655</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44656</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44658</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44663</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>44663</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44671</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44671</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44684</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44684</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>44691</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>44693</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44693</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44694</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44694</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44701</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44706</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44706</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>44708</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>44713</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44720</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44733</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44733</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44734</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>44735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44735</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>44739</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>44741</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44749</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44750</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44756</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44756</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44757</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44763</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44767</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44775</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>44775</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>44776</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44782</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44785</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44785</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44788</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44790</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44795</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44796</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>44800</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44802</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44804</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44804</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44805</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44805</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44810</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44810</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44813</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44813</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44817</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>44818</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>44820</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44823</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44823</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44824</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44827</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44830</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>44840</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>44840</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44841</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44845</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44845</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44846</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44845</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44846</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44848</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44853</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>44853</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>44859</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>44862</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>44865</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44865</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44867</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44867</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>44868</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44869</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>44874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44874</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44876</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44876</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44881</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44882</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>44882</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>44885</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44886</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>44886</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>44887</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44888</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>44889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>44895</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44895</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>44896</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44896</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>44897</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44904</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>44904</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44907</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>44910</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>44910</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>44911</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>44916</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>44922</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>44922</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>44927</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>44935</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>44935</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>44936</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>44936</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44937</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44937</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>44942</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44943</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44944</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44946</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>44951</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44959</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44959</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44960</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44962</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44962</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44967</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44970</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44971</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44972</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>44973</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>44973</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44979</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44979</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44985</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>44985</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44986</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44988</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44991</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44991</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>44992</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44994</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44995</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44999</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45006</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45009</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45012</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45012</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45014</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45014</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45015</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45015</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45019</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45019</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45022</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45026</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45027</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45027</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45029</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45029</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45030</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45030</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45034</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45034</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45036</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45036</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45040</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45040</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45054</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45054</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45056</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45058</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45069</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45070</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45071</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45071</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45072</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45072</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45079</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45082</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45082</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45084</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45084</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45085</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45086</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45086</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45089</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45089</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45090</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45090</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45096</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45098</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>45103</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45104</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45104</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45106</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45107</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45113</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45113</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45117</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45120</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45120</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45125</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45133</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45133</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45138</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45138</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45141</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45141</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45146</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45146</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45152</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45152</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45156</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45156</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45159</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45159</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45161</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45161</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45162</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45162</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45168</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45169</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45169</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45182</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45184</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45184</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45188</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45192</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45192</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>45194</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45194</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45195</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45196</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45197</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45198</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45203</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45203</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>45204</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45204</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45205</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45208</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45209</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45209</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45211</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45212</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45212</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45217</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45217</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45218</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45218</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45219</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45219</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45220</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45223</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45223</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45224</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45229</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>45229</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45232</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45232</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45238</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45239</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45240</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45243</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45243</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45245</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45245</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45247</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45250</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45252</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45252</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45253</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45253</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45255</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45257</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45257</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45259</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45264</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45265</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45267</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45267</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45272</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45272</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45278</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45278</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45279</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45282</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45282</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45293</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45295</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45300</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45301</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45302</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>45302</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45303</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52737,7 +52737,7 @@
         <v>45306</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45308</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45308</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45312</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45312</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45317</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45317</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45319</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45320</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45322</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         <v>45324</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>45324</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45328</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45329</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45330</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45330</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53756,14 +53756,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 5605-2024</t>
+          <t>A 5633-2024</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -53813,14 +53813,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 5633-2024</t>
+          <t>A 5605-2024</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -53877,7 +53877,7 @@
         <v>45335</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45338</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53984,14 +53984,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 7297-2024</t>
+          <t>A 7298-2024</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="H887" t="n">
         <v>0</v>
@@ -54041,14 +54041,14 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>A 7298-2024</t>
+          <t>A 7297-2024</t>
         </is>
       </c>
       <c r="B888" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z888"/>
+  <dimension ref="A1:Z894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45344</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>43332</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>43348</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>43360</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43382</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43403</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>43411</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>43413</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>43424</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>43426</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>43430</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>43447</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>43453</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43478</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>43489</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>43493</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>43502</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>43508</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>43509</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>43510</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43511</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>43530</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>43537</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43559</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43565</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43567</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43579</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43588</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>43612</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>43614</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43623</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>43626</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43635</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43650</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43651</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43706</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>43718</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43721</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43732</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43755</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43759</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43761</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43763</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43767</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43770</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43776</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43777</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43783</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43788</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>43790</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43794</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43809</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43811</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>43812</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43818</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>43838</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>43850</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43852</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>43854</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>43855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>43865</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>43871</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>43872</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>43873</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>43879</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>43895</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>43896</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>43901</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>43906</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>43927</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>43936</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>43942</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>43951</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43955</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>43959</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43962</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>43978</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43979</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43980</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43990</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43997</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44000</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44005</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44006</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44008</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44011</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44014</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44015</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44022</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44025</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44026</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44043</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44056</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44060</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44062</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>44067</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44078</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44081</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44084</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44095</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44096</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44098</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>44109</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44112</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44118</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44126</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44127</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44134</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44140</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44144</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44146</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44147</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44152</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44154</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44158</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44161</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44162</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44175</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44176</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>44191</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44192</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44196</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44200</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44204</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44216</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44228</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44231</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44235</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44252</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44258</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44260</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44263</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44270</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44271</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44272</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44274</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44277</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>44278</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44279</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44281</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44284</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44286</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44294</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44295</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44300</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44305</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44307</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44308</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44319</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44321</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44326</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44333</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44334</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44336</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44342</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44343</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44347</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44349</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44350</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44351</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44354</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44356</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44361</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44364</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>44369</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44370</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44376</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44377</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44390</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44414</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44418</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44419</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44421</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44427</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>44437</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44438</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44439</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44446</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44448</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44452</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44459</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44461</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44468</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44473</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44488</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44490</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44491</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44494</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44496</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44497</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44498</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44502</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44516</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44517</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44523</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44526</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44533</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44538</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44539</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44543</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44545</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>44546</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44546</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44557</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44560</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>44571</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44573</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>44579</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44585</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44586</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44586</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44588</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44589</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44589</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44599</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44600</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44603</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44603</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44606</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44606</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44616</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44616</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44628</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44629</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44631</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>44634</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44635</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44636</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44637</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44641</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44651</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44651</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44655</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44656</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44658</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44663</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>44663</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44671</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44671</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44684</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44684</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>44691</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>44693</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44693</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44694</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44694</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44701</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44706</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44706</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>44708</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>44713</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44720</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44733</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44733</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44734</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>44735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44735</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>44739</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>44741</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44749</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44750</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44756</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44756</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44757</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44763</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44767</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44775</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>44775</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>44776</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44782</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44785</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44785</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44788</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44790</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44795</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44796</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>44800</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44802</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44804</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44804</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44805</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44805</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44810</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44810</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44813</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44813</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44817</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>44818</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>44820</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44823</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44823</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44824</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44827</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44830</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>44840</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>44840</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44841</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44845</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44845</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44846</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44845</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44846</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44848</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44853</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>44853</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>44859</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>44862</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>44865</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44865</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44867</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44867</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>44868</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44869</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>44874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44874</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44876</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44876</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44881</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44882</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>44882</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>44885</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44886</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>44886</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>44887</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44888</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>44889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>44895</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44895</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>44896</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44896</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>44897</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44904</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>44904</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44907</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>44910</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>44910</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>44911</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>44916</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>44922</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>44922</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>44927</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>44935</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>44935</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>44936</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>44936</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44937</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44937</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>44942</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44943</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44944</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44946</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>44951</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44959</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44959</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44960</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44962</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44962</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44967</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44970</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44971</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44972</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>44973</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>44973</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44979</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44979</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44985</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>44985</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44986</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44988</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44991</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44991</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>44992</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44994</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44995</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44999</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45006</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45009</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45012</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45012</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45014</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45014</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45015</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45015</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45019</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45019</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45022</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45026</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45027</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45027</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45029</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45029</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45030</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45030</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45034</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45034</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45036</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45036</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45040</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45040</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45054</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45054</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45056</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45058</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45069</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45070</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45071</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45071</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45072</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45072</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45079</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45082</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45082</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45084</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45084</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45085</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45086</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45086</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45089</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45089</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45090</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45090</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45096</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45098</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>45103</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45104</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45104</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45106</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45107</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45113</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45113</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45117</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45120</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45120</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45125</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45133</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45133</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45138</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45138</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45141</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45141</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45146</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45146</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45152</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45152</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45156</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45156</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45159</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45159</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45161</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45161</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45162</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45162</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45168</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45169</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45169</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45182</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45184</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45184</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45188</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45192</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45192</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>45194</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45194</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45195</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45196</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45197</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45198</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45203</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45203</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>45204</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45204</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45205</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45208</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45209</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45209</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45211</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45212</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45212</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45217</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45217</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45218</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45218</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45219</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45219</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45220</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45223</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45223</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45224</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45229</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>45229</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45232</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45232</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45238</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45239</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45240</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45243</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45243</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45245</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45245</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45247</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45250</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45252</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45252</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45253</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45253</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45255</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45257</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45257</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45259</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45264</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45265</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45267</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45267</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45272</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45272</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45278</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45278</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45279</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45282</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45282</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45293</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45295</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45300</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45301</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45302</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>45302</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45303</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52737,7 +52737,7 @@
         <v>45306</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45308</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45308</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45312</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45312</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45317</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45317</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45319</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45320</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45322</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53357,14 +53357,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 4287-2024</t>
+          <t>A 4290-2024</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53377,7 +53377,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -53414,14 +53414,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 4290-2024</t>
+          <t>A 4294-2024</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53434,7 +53434,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -53471,14 +53471,14 @@
     <row r="878" ht="15" customHeight="1">
       <c r="A878" t="inlineStr">
         <is>
-          <t>A 4294-2024</t>
+          <t>A 4287-2024</t>
         </is>
       </c>
       <c r="B878" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53491,7 +53491,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -53535,7 +53535,7 @@
         <v>45328</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45329</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45330</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45330</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53756,14 +53756,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 5633-2024</t>
+          <t>A 5605-2024</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -53813,14 +53813,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 5605-2024</t>
+          <t>A 5633-2024</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -53877,7 +53877,7 @@
         <v>45335</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45338</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53984,14 +53984,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 7298-2024</t>
+          <t>A 7297-2024</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="H887" t="n">
         <v>0</v>
@@ -54038,62 +54038,404 @@
       </c>
       <c r="R887" s="2" t="inlineStr"/>
     </row>
-    <row r="888">
+    <row r="888" ht="15" customHeight="1">
       <c r="A888" t="inlineStr">
         <is>
-          <t>A 7297-2024</t>
+          <t>A 7298-2024</t>
         </is>
       </c>
       <c r="B888" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C888" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>GÄVLE</t>
+        </is>
+      </c>
+      <c r="G888" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H888" t="n">
+        <v>0</v>
+      </c>
+      <c r="I888" t="n">
+        <v>0</v>
+      </c>
+      <c r="J888" t="n">
+        <v>0</v>
+      </c>
+      <c r="K888" t="n">
+        <v>0</v>
+      </c>
+      <c r="L888" t="n">
+        <v>0</v>
+      </c>
+      <c r="M888" t="n">
+        <v>0</v>
+      </c>
+      <c r="N888" t="n">
+        <v>0</v>
+      </c>
+      <c r="O888" t="n">
+        <v>0</v>
+      </c>
+      <c r="P888" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q888" t="n">
+        <v>0</v>
+      </c>
+      <c r="R888" s="2" t="inlineStr"/>
+    </row>
+    <row r="889" ht="15" customHeight="1">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>A 7923-2024</t>
+        </is>
+      </c>
+      <c r="B889" s="1" t="n">
         <v>45350</v>
       </c>
-      <c r="D888" t="inlineStr">
-        <is>
-          <t>GÄVLEBORGS LÄN</t>
-        </is>
-      </c>
-      <c r="E888" t="inlineStr">
-        <is>
-          <t>GÄVLE</t>
-        </is>
-      </c>
-      <c r="G888" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H888" t="n">
-        <v>0</v>
-      </c>
-      <c r="I888" t="n">
-        <v>0</v>
-      </c>
-      <c r="J888" t="n">
-        <v>0</v>
-      </c>
-      <c r="K888" t="n">
-        <v>0</v>
-      </c>
-      <c r="L888" t="n">
-        <v>0</v>
-      </c>
-      <c r="M888" t="n">
-        <v>0</v>
-      </c>
-      <c r="N888" t="n">
-        <v>0</v>
-      </c>
-      <c r="O888" t="n">
-        <v>0</v>
-      </c>
-      <c r="P888" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q888" t="n">
-        <v>0</v>
-      </c>
-      <c r="R888" s="2" t="inlineStr"/>
+      <c r="C889" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>GÄVLE</t>
+        </is>
+      </c>
+      <c r="G889" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H889" t="n">
+        <v>0</v>
+      </c>
+      <c r="I889" t="n">
+        <v>0</v>
+      </c>
+      <c r="J889" t="n">
+        <v>0</v>
+      </c>
+      <c r="K889" t="n">
+        <v>0</v>
+      </c>
+      <c r="L889" t="n">
+        <v>0</v>
+      </c>
+      <c r="M889" t="n">
+        <v>0</v>
+      </c>
+      <c r="N889" t="n">
+        <v>0</v>
+      </c>
+      <c r="O889" t="n">
+        <v>0</v>
+      </c>
+      <c r="P889" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q889" t="n">
+        <v>0</v>
+      </c>
+      <c r="R889" s="2" t="inlineStr"/>
+    </row>
+    <row r="890" ht="15" customHeight="1">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>A 7915-2024</t>
+        </is>
+      </c>
+      <c r="B890" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C890" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>GÄVLE</t>
+        </is>
+      </c>
+      <c r="G890" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H890" t="n">
+        <v>0</v>
+      </c>
+      <c r="I890" t="n">
+        <v>0</v>
+      </c>
+      <c r="J890" t="n">
+        <v>0</v>
+      </c>
+      <c r="K890" t="n">
+        <v>0</v>
+      </c>
+      <c r="L890" t="n">
+        <v>0</v>
+      </c>
+      <c r="M890" t="n">
+        <v>0</v>
+      </c>
+      <c r="N890" t="n">
+        <v>0</v>
+      </c>
+      <c r="O890" t="n">
+        <v>0</v>
+      </c>
+      <c r="P890" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q890" t="n">
+        <v>0</v>
+      </c>
+      <c r="R890" s="2" t="inlineStr"/>
+    </row>
+    <row r="891" ht="15" customHeight="1">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>A 7899-2024</t>
+        </is>
+      </c>
+      <c r="B891" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C891" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>GÄVLE</t>
+        </is>
+      </c>
+      <c r="G891" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H891" t="n">
+        <v>0</v>
+      </c>
+      <c r="I891" t="n">
+        <v>0</v>
+      </c>
+      <c r="J891" t="n">
+        <v>0</v>
+      </c>
+      <c r="K891" t="n">
+        <v>0</v>
+      </c>
+      <c r="L891" t="n">
+        <v>0</v>
+      </c>
+      <c r="M891" t="n">
+        <v>0</v>
+      </c>
+      <c r="N891" t="n">
+        <v>0</v>
+      </c>
+      <c r="O891" t="n">
+        <v>0</v>
+      </c>
+      <c r="P891" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q891" t="n">
+        <v>0</v>
+      </c>
+      <c r="R891" s="2" t="inlineStr"/>
+    </row>
+    <row r="892" ht="15" customHeight="1">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>A 7920-2024</t>
+        </is>
+      </c>
+      <c r="B892" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C892" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>GÄVLE</t>
+        </is>
+      </c>
+      <c r="G892" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H892" t="n">
+        <v>0</v>
+      </c>
+      <c r="I892" t="n">
+        <v>0</v>
+      </c>
+      <c r="J892" t="n">
+        <v>0</v>
+      </c>
+      <c r="K892" t="n">
+        <v>0</v>
+      </c>
+      <c r="L892" t="n">
+        <v>0</v>
+      </c>
+      <c r="M892" t="n">
+        <v>0</v>
+      </c>
+      <c r="N892" t="n">
+        <v>0</v>
+      </c>
+      <c r="O892" t="n">
+        <v>0</v>
+      </c>
+      <c r="P892" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q892" t="n">
+        <v>0</v>
+      </c>
+      <c r="R892" s="2" t="inlineStr"/>
+    </row>
+    <row r="893" ht="15" customHeight="1">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>A 7926-2024</t>
+        </is>
+      </c>
+      <c r="B893" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C893" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>GÄVLE</t>
+        </is>
+      </c>
+      <c r="G893" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H893" t="n">
+        <v>0</v>
+      </c>
+      <c r="I893" t="n">
+        <v>0</v>
+      </c>
+      <c r="J893" t="n">
+        <v>0</v>
+      </c>
+      <c r="K893" t="n">
+        <v>0</v>
+      </c>
+      <c r="L893" t="n">
+        <v>0</v>
+      </c>
+      <c r="M893" t="n">
+        <v>0</v>
+      </c>
+      <c r="N893" t="n">
+        <v>0</v>
+      </c>
+      <c r="O893" t="n">
+        <v>0</v>
+      </c>
+      <c r="P893" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q893" t="n">
+        <v>0</v>
+      </c>
+      <c r="R893" s="2" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>A 8031-2024</t>
+        </is>
+      </c>
+      <c r="B894" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C894" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>GÄVLE</t>
+        </is>
+      </c>
+      <c r="G894" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H894" t="n">
+        <v>0</v>
+      </c>
+      <c r="I894" t="n">
+        <v>0</v>
+      </c>
+      <c r="J894" t="n">
+        <v>0</v>
+      </c>
+      <c r="K894" t="n">
+        <v>0</v>
+      </c>
+      <c r="L894" t="n">
+        <v>0</v>
+      </c>
+      <c r="M894" t="n">
+        <v>0</v>
+      </c>
+      <c r="N894" t="n">
+        <v>0</v>
+      </c>
+      <c r="O894" t="n">
+        <v>0</v>
+      </c>
+      <c r="P894" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q894" t="n">
+        <v>0</v>
+      </c>
+      <c r="R894" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45344</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>43332</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>43348</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>43360</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43382</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43403</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>43411</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>43413</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>43424</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>43426</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>43430</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>43447</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>43453</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43478</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>43489</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>43493</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>43502</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>43508</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>43509</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>43510</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43511</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>43530</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>43537</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43559</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43565</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43567</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43579</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43588</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>43612</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>43614</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43623</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>43626</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43635</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43650</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43651</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43706</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>43718</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43721</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43732</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43755</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43759</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43761</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43763</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43767</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43770</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43776</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43777</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43783</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43788</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>43790</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43794</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43809</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43811</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>43812</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43818</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>43838</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>43850</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43852</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>43854</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>43855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>43865</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>43871</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>43872</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>43873</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>43879</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>43895</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>43896</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>43901</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>43906</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>43927</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>43936</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>43942</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>43951</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43955</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>43959</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43962</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>43978</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43979</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43980</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43990</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43997</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44000</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44005</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44006</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44008</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44011</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44014</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44015</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44022</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44025</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44026</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44043</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44056</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44060</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44062</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>44067</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44078</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44081</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44084</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44095</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44096</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44098</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>44109</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44112</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44118</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44126</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44127</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44134</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44140</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44144</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44146</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44147</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44152</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44154</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44158</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44161</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44162</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44175</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44176</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>44191</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44192</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44196</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44200</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44204</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44216</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44228</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44231</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44235</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44252</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44258</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44260</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44263</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44270</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44271</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44272</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44274</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44277</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>44278</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44279</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44281</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44284</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44286</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44294</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44295</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44300</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44305</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44307</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44308</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44319</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44321</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44326</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44333</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44334</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44336</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44342</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44343</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44347</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44349</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44350</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44351</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44354</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44356</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44361</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44364</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>44369</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44370</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44376</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44377</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44390</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44414</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44418</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44419</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44421</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44427</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>44437</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44438</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44439</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44446</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44448</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44452</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44459</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44461</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44468</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44473</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44488</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44490</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44491</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44494</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44496</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44497</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44498</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44502</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44516</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44517</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44523</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44526</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44533</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44538</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44539</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44543</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44545</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>44546</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44546</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44557</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44560</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>44571</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44573</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>44579</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44585</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44586</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44586</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44588</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44589</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44589</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44599</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44600</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44603</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44603</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44606</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44606</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44616</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44616</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44628</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44629</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44631</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>44634</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44635</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44636</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44637</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44641</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44651</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44651</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44655</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44656</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44658</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44663</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>44663</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44671</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44671</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44684</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44684</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>44691</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>44693</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44693</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44694</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44694</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44701</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44706</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44706</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>44708</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>44713</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44720</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44733</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44733</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44734</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>44735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44735</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>44739</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>44741</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44749</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44750</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44756</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44756</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44757</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44763</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44767</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44775</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>44775</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>44776</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44782</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44785</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44785</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44788</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44790</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44795</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44796</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>44800</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44802</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44804</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44804</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44805</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44805</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44810</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44810</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44813</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44813</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44817</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>44818</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>44820</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44823</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44823</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44824</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44827</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44830</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>44840</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>44840</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44841</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44845</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44845</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44846</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44845</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44846</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44848</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44853</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>44853</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>44859</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>44862</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>44865</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44865</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44867</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44867</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>44868</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44869</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>44874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44874</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44876</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44876</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44881</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44882</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>44882</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>44885</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44886</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>44886</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>44887</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44888</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>44889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>44895</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44895</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>44896</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44896</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>44897</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44904</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>44904</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44907</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>44910</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>44910</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>44911</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>44916</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>44922</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>44922</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>44927</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>44935</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>44935</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>44936</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>44936</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44937</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44937</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>44942</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44943</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44944</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44946</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>44951</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44959</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44959</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44960</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44962</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44962</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44967</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44970</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44971</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44972</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>44973</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>44973</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44979</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44979</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44985</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>44985</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44986</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44988</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44991</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44991</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>44992</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44994</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44995</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44999</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45006</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45009</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45012</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45012</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45014</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45014</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45015</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45015</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45019</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45019</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45022</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45026</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45027</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45027</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45029</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45029</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45030</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45030</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45034</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45034</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45036</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45036</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45040</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45040</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45054</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45054</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45056</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45058</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45069</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45070</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45071</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45071</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45072</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45072</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45079</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45082</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45082</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45084</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45084</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45085</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45086</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45086</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45089</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45089</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45090</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45090</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45096</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45098</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>45103</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45104</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45104</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45106</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45107</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45113</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45113</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45117</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45120</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45120</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45125</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45133</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45133</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45138</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45138</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45141</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45141</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45146</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45146</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45152</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45152</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45156</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45156</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45159</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45159</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45161</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45161</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45162</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45162</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45168</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45169</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45169</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45182</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45184</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45184</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45188</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45192</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45192</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>45194</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45194</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45195</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45196</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45197</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45198</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45203</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45203</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>45204</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45204</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45205</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45208</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45209</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45209</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45211</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45212</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45212</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45217</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45217</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45218</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45218</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45219</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45219</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45220</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45223</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45223</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45224</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45229</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>45229</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45232</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45232</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45238</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45239</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45240</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45243</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45243</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45245</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45245</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45247</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45250</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45252</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45252</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45253</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45253</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45255</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45257</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45257</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45259</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45264</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45265</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45267</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45267</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45272</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45272</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45278</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45278</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45279</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45282</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45282</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45293</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45295</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45300</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45301</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45302</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>45302</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45303</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52737,7 +52737,7 @@
         <v>45306</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45308</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45308</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45312</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45312</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45317</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45317</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45319</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45320</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45322</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53357,14 +53357,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 4290-2024</t>
+          <t>A 4287-2024</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53377,7 +53377,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -53414,14 +53414,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 4294-2024</t>
+          <t>A 4290-2024</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53434,7 +53434,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -53471,14 +53471,14 @@
     <row r="878" ht="15" customHeight="1">
       <c r="A878" t="inlineStr">
         <is>
-          <t>A 4287-2024</t>
+          <t>A 4294-2024</t>
         </is>
       </c>
       <c r="B878" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53491,7 +53491,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -53535,7 +53535,7 @@
         <v>45328</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45329</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45330</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45330</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53756,14 +53756,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 5605-2024</t>
+          <t>A 5633-2024</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -53813,14 +53813,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 5633-2024</t>
+          <t>A 5605-2024</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -53877,7 +53877,7 @@
         <v>45335</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45338</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53984,14 +53984,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 7297-2024</t>
+          <t>A 7298-2024</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="H887" t="n">
         <v>0</v>
@@ -54041,14 +54041,14 @@
     <row r="888" ht="15" customHeight="1">
       <c r="A888" t="inlineStr">
         <is>
-          <t>A 7298-2024</t>
+          <t>A 7297-2024</t>
         </is>
       </c>
       <c r="B888" s="1" t="n">
         <v>45344</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -54098,14 +54098,14 @@
     <row r="889" ht="15" customHeight="1">
       <c r="A889" t="inlineStr">
         <is>
-          <t>A 7923-2024</t>
+          <t>A 7920-2024</t>
         </is>
       </c>
       <c r="B889" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="H889" t="n">
         <v>0</v>
@@ -54155,14 +54155,14 @@
     <row r="890" ht="15" customHeight="1">
       <c r="A890" t="inlineStr">
         <is>
-          <t>A 7915-2024</t>
+          <t>A 7926-2024</t>
         </is>
       </c>
       <c r="B890" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54175,7 +54175,7 @@
         </is>
       </c>
       <c r="G890" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -54219,7 +54219,7 @@
         <v>45350</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54269,14 +54269,14 @@
     <row r="892" ht="15" customHeight="1">
       <c r="A892" t="inlineStr">
         <is>
-          <t>A 7920-2024</t>
+          <t>A 7915-2024</t>
         </is>
       </c>
       <c r="B892" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -54326,14 +54326,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 7926-2024</t>
+          <t>A 7923-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -54390,7 +54390,7 @@
         <v>45350</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45344</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>43332</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>43348</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>43360</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43382</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43403</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>43411</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>43413</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>43424</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>43426</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>43430</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>43447</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>43453</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43478</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>43489</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>43493</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>43502</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>43508</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>43509</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>43510</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43511</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>43530</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>43537</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43559</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43565</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43567</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43579</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43588</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>43612</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>43614</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43623</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>43626</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43635</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43650</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43651</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43706</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>43718</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43721</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43732</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43755</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43759</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43761</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43763</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43767</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43770</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43776</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43777</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43783</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43788</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>43790</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43794</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43809</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43811</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>43812</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43818</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>43838</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>43850</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43852</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>43854</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>43855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>43865</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>43871</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>43872</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>43873</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>43879</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>43895</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>43896</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>43901</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>43906</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>43927</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>43936</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>43942</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>43951</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43955</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>43959</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43962</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>43978</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43979</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43980</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43990</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43997</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44000</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44005</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44006</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44008</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44011</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44014</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44015</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44022</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44025</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44026</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44043</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44056</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44060</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44062</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>44067</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44078</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44081</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44084</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44095</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44096</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44098</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>44109</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44112</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44118</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44126</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44127</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44134</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44140</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44144</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44146</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44147</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44152</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44154</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44158</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44161</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44162</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44175</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44176</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>44191</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44192</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44196</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44200</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44204</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44216</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44228</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44231</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44235</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44252</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44258</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44260</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44263</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44270</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44271</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44272</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44274</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44277</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>44278</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44279</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44281</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44284</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44286</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44294</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44295</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44300</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44305</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44307</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44308</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44319</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44321</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44326</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44333</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44334</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44336</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44342</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44343</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44347</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44349</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44350</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44351</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44354</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44356</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44361</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44364</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>44369</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44370</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44376</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44377</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44390</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44414</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44418</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44419</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44421</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44427</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>44437</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44438</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44439</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44446</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44448</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44452</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44459</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44461</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44468</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44473</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44488</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44490</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44491</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44494</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44496</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44497</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44498</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44502</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44516</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44517</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44523</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44526</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44533</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44538</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44539</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44543</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>44545</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>44546</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>44546</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44546</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44557</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44560</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>44571</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44573</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>44579</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>44580</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>44585</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44585</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>44586</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>44586</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44586</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44588</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44589</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44589</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44594</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44599</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44599</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44599</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44600</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>44603</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44603</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44606</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44606</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44616</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44616</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44628</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44629</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44629</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44629</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44631</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>44634</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44635</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44636</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44636</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44637</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44641</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44651</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44651</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44655</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44656</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44658</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>44663</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44663</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>44663</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>44671</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44671</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44671</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44684</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44684</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44684</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44684</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>44691</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>44693</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44693</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44694</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44694</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44701</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44706</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44706</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>44708</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>44713</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44720</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44733</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>44733</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44733</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44734</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44735</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44735</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>44735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>44735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44735</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>44739</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>44741</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44749</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44750</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44756</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44756</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44756</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44756</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44756</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44757</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44763</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44767</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44775</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44775</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>44775</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>44776</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>44782</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44785</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>44785</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44788</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44790</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>44795</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44796</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>44800</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44802</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44804</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44804</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44805</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44805</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>44810</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44810</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44810</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>44813</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31604,7 +31604,7 @@
         <v>44813</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44817</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>44818</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>44820</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44823</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31899,7 +31899,7 @@
         <v>44823</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>44824</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44827</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44830</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>44840</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>44840</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44841</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>44845</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44845</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44846</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>44845</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44846</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>44848</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44853</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>44853</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>44859</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32836,7 +32836,7 @@
         <v>44862</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>44865</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44865</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44867</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44867</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33136,7 +33136,7 @@
         <v>44868</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>44869</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44874</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33322,7 +33322,7 @@
         <v>44874</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>44874</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>44876</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>44876</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>44881</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>44882</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>44882</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>44882</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>44882</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>44885</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>44886</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>44886</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>44887</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>44888</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>44889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>44889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>44895</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44895</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>44896</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44896</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>44897</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>44904</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44904</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>44904</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>44904</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44907</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>44910</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35050,7 +35050,7 @@
         <v>44910</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>44910</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>44910</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>44911</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>44916</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         <v>44922</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>44922</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>44922</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>44927</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>44928</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         <v>44935</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35682,7 +35682,7 @@
         <v>44935</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>44935</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>44936</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>44936</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>44937</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>44937</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>44942</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>44942</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44943</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44944</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>44946</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>44951</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>44951</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>44951</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>44951</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44959</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>44959</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>44959</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>44959</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44959</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44959</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44959</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>44959</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44959</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44959</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44959</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44959</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44959</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>44959</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>44960</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44962</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44962</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44967</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>44967</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>44970</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>44971</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44972</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>44973</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>44973</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>44979</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44979</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>44985</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>44985</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44986</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44988</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>44991</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>44991</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>44992</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44994</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>44995</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44999</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45006</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45009</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>45012</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45012</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45014</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45014</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39113,7 +39113,7 @@
         <v>45014</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45014</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45015</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45015</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45015</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45015</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45015</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45019</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45019</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45019</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45022</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45022</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>45022</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45022</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39956,7 +39956,7 @@
         <v>45026</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45027</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>45027</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>45029</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45029</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45029</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45030</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45030</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45030</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>45034</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45034</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45034</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45036</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45036</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40799,7 +40799,7 @@
         <v>45040</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45040</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45040</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45044</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45054</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45054</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45056</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45058</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45069</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45070</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45071</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45071</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45072</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>45072</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>45079</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45082</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45082</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45084</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45084</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45085</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45086</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45086</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45089</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42217,7 +42217,7 @@
         <v>45089</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45089</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45089</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45089</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>45089</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45090</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45090</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45090</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45096</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45098</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42802,7 +42802,7 @@
         <v>45103</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45104</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45104</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45104</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>45104</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45104</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45106</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45107</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45107</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45107</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45113</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45113</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45117</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45120</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45120</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45125</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>45133</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45133</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45133</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45138</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>45138</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45141</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45141</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45146</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>45146</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>45152</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44376,7 +44376,7 @@
         <v>45152</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44438,7 +44438,7 @@
         <v>45156</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45156</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45159</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45159</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45159</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>45159</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45161</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45161</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45162</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>45162</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45168</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>45169</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45169</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45169</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45169</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45176</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45176</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45176</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45176</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45182</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45182</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45184</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45184</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45188</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45192</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45192</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45970,7 +45970,7 @@
         <v>45194</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45194</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45195</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>45195</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45195</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45196</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45197</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45198</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>45203</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45203</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>45203</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45203</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45203</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>45204</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45204</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45205</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45208</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45209</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45209</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45209</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>45211</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45212</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45212</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>45212</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45217</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47430,7 +47430,7 @@
         <v>45217</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45217</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45218</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>45218</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47663,7 +47663,7 @@
         <v>45218</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45219</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45219</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45220</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45223</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45223</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45224</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45229</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>45229</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>45231</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45232</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45232</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45232</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48429,7 +48429,7 @@
         <v>45232</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45232</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45232</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45232</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45232</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45238</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45239</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45240</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45243</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>45243</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>45243</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45243</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45243</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45245</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49371,7 +49371,7 @@
         <v>45245</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>45245</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45245</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45245</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49609,7 +49609,7 @@
         <v>45245</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45245</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45245</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45247</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>45250</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45252</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45252</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45253</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45253</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45253</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45255</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45257</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>45257</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45257</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45257</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45257</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45259</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45261</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45261</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>45264</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45264</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50841,7 +50841,7 @@
         <v>45264</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45265</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50955,7 +50955,7 @@
         <v>45266</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45266</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51069,7 +51069,7 @@
         <v>45266</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45266</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51183,7 +51183,7 @@
         <v>45266</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45266</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45267</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51411,7 +51411,7 @@
         <v>45267</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45272</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>45272</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
         <v>45278</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>45278</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>45279</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45282</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45282</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51867,7 +51867,7 @@
         <v>45282</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45282</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45282</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45282</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45293</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45293</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45293</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45293</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45295</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45300</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45301</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45302</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>45302</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45303</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52737,7 +52737,7 @@
         <v>45306</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45308</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45308</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>45312</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45312</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>45312</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45317</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>45317</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45319</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45320</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53307,7 +53307,7 @@
         <v>45322</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>45324</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         <v>45324</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>45324</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45328</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45329</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45330</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45330</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53756,14 +53756,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 5633-2024</t>
+          <t>A 5605-2024</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -53813,14 +53813,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 5605-2024</t>
+          <t>A 5633-2024</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -53877,7 +53877,7 @@
         <v>45335</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45338</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45344</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45344</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54098,14 +54098,14 @@
     <row r="889" ht="15" customHeight="1">
       <c r="A889" t="inlineStr">
         <is>
-          <t>A 7920-2024</t>
+          <t>A 7923-2024</t>
         </is>
       </c>
       <c r="B889" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         </is>
       </c>
       <c r="G889" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="H889" t="n">
         <v>0</v>
@@ -54155,14 +54155,14 @@
     <row r="890" ht="15" customHeight="1">
       <c r="A890" t="inlineStr">
         <is>
-          <t>A 7926-2024</t>
+          <t>A 7899-2024</t>
         </is>
       </c>
       <c r="B890" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54175,7 +54175,7 @@
         </is>
       </c>
       <c r="G890" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -54212,14 +54212,14 @@
     <row r="891" ht="15" customHeight="1">
       <c r="A891" t="inlineStr">
         <is>
-          <t>A 7899-2024</t>
+          <t>A 7920-2024</t>
         </is>
       </c>
       <c r="B891" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         </is>
       </c>
       <c r="G891" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -54269,14 +54269,14 @@
     <row r="892" ht="15" customHeight="1">
       <c r="A892" t="inlineStr">
         <is>
-          <t>A 7915-2024</t>
+          <t>A 7926-2024</t>
         </is>
       </c>
       <c r="B892" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54289,7 +54289,7 @@
         </is>
       </c>
       <c r="G892" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -54326,14 +54326,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 7923-2024</t>
+          <t>A 7915-2024</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45350</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         </is>
       </c>
       <c r="G893" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -54390,7 +54390,7 @@
         <v>45350</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>

--- a/Översikt GÄVLE.xlsx
+++ b/Översikt GÄVLE.xlsx
@@ -569,7 +569,7 @@
         <v>43928</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>44494</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45013</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>43812</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>44840</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>45302</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>43721</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>45257</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45302</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>43812</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45121</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45281</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>44272</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>44314</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44323</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45019</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45029</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45041</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45055</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45117</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45281</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>45338</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>43588</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>44144</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44160</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>44279</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>44490</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44602</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44658</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44721</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44790</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>44811</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44977</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>45120</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>45243</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45344</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>43332</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>43348</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>43360</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>43382</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43403</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>43411</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>43411</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>43413</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>43418</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>43418</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>43423</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>43424</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>43426</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>43430</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>43430</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>43431</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>43447</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>43447</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>43447</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>43447</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>43447</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>43453</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>43454</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>43473</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>43476</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>43478</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>43479</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>43480</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>43481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>43482</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>43486</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>43486</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>43486</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>43489</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>43489</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>43489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>43489</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>43493</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>43495</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>43502</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>43508</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>43509</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>43510</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>43511</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>43530</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>43537</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>43559</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>43559</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>43565</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>43567</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>43567</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>43578</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>43579</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>43588</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>43588</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>43588</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>43612</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>43614</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>43623</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>43626</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>43635</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>43635</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>43650</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>43651</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>43696</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>43706</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>43707</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>43718</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>43719</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>43719</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>43721</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>43728</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>43728</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>43728</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>43732</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>43735</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>43746</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>43755</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>43759</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>43761</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43761</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>43763</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>43767</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>43770</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43770</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         <v>43776</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>43777</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>43777</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43783</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43788</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>43790</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43794</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43808</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43809</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43811</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43812</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>43812</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>43818</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>43818</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>43838</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>43850</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>43852</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>43854</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>43854</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>43854</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>43855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>43865</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>43871</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>43872</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>43873</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>43873</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>43873</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>43879</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>43879</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>43888</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>43889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>43895</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>43896</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>43901</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>43906</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>43927</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>43936</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>43942</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>43951</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>43955</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>43959</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>43962</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>43978</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>43979</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>43980</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>43990</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>43990</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>43990</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43997</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>44000</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>44000</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44005</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>44006</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44008</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44011</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44014</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44015</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         <v>44015</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44022</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44025</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44026</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44043</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44056</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44056</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44056</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44060</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>44060</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44062</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>44067</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>44068</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>44068</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>44069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44076</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44076</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44078</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44081</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44081</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44084</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44095</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>44095</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>44095</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44095</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>44096</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>44096</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>44098</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>44109</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>44112</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44112</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44118</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44125</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44126</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44126</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44127</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44127</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44127</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44127</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44134</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44140</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44140</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44140</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44144</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44146</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44147</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44152</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44154</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44154</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44158</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44158</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44160</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44161</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44162</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44175</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>44176</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44176</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>44191</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>44191</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>44192</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>44192</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44192</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44192</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44192</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>44192</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44192</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44192</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44196</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>44200</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>44200</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44204</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44216</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44223</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44228</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44231</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44235</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>44235</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44252</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>44252</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44258</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44258</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44260</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44263</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44263</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44270</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>44271</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>44271</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44272</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44272</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44274</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44274</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>44277</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>44278</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44279</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44279</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44281</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>44284</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44284</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44286</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44286</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>44286</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>44286</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>44294</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>44294</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44294</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>44295</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>44300</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19786,7 +19786,7 @@
         <v>44300</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44300</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>44305</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44307</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44308</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44308</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44319</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44321</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44321</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44326</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>44333</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>44334</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44336</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44342</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44342</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>44342</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44343</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44347</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44349</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44349</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>44350</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44351</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44351</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44354</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44356</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44361</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44364</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>44364</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44369</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>44369</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>44370</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>44370</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44376</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>44377</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>44389</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44390</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44390</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44414</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44418</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44419</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44421</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>44427</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>44437</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>44438</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44439</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>44446</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44448</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44452</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44455</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>44455</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44459</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44461</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>44462</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>44466</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>44466</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44468</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44473</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44488</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44488</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44490</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>44491</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44491</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44494</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>44496</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44497</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44498</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>44498</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44498</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44502</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44516</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>44517</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44518</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44519</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44519</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44523</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44526</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24556,7 +24556,7 @@
         <v>44533</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44538</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>44539</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44539</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>44543</v>
       </c>
       <c r=